--- a/DataAnalysis/DataAnalysis.xlsx
+++ b/DataAnalysis/DataAnalysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5967B9-A949-4225-BC48-6F1DB7C8D68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63E8C7D-1A33-4E37-B489-AF459867001E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{216728D3-2A76-4D61-AF39-758D90BA286A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{216728D3-2A76-4D61-AF39-758D90BA286A}"/>
   </bookViews>
   <sheets>
     <sheet name="DataAnalysis" sheetId="1" r:id="rId1"/>
@@ -1239,91 +1239,89 @@
         <v>21</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="T4">
-        <f>AVERAGE(R4,S4)</f>
-        <v>12</v>
+        <f>AVERAGE(R4:S4)</f>
+        <v>25.5</v>
       </c>
       <c r="U4">
         <f>AVERAGE(T4:T46)</f>
-        <v>16.166666666666668</v>
+        <v>25.5</v>
       </c>
       <c r="V4">
         <f>_xlfn.STDEV.P(T4:T46)</f>
-        <v>4.2491829279939877</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <f>AVERAGE(W4,X4)</f>
-        <v>12.5</v>
+        <f>AVERAGE(W4:X4)</f>
+        <v>30.5</v>
       </c>
       <c r="Z4">
-        <f>AVERAGE(Y4:Y46)</f>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AA4">
-        <f>_xlfn.STDEV.P(Y4:Y46)</f>
-        <v>1.2247448713915889</v>
+        <v>22</v>
       </c>
       <c r="AB4">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="AC4">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="AD4">
-        <f>AVERAGE(AB4,AC4)</f>
-        <v>12.5</v>
+        <f>AVERAGE(AB4:AC4)</f>
+        <v>45</v>
       </c>
       <c r="AE4">
         <f>AVERAGE(AD4:AD46)</f>
-        <v>16.833333333333332</v>
+        <v>45</v>
       </c>
       <c r="AF4">
         <f>_xlfn.STDEV.P(AD4:AD46)</f>
-        <v>4.7842333648024411</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <f>AVERAGE(T4,Y4,AD4)</f>
-        <v>12.333333333333334</v>
+        <v>33.666666666666664</v>
       </c>
       <c r="AI4">
         <f>AVERAGE(AH4:AH46)</f>
-        <v>15.666666666666666</v>
+        <v>33.666666666666664</v>
       </c>
       <c r="AJ4">
         <f>_xlfn.STDEV.P(AH4:AH46)</f>
-        <v>3.39934634239519</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <f>MIN(T4,Y4,AD4)</f>
-        <v>12</v>
+        <v>25.5</v>
       </c>
       <c r="AM4">
         <f>AVERAGE(AL4:AL46)</f>
-        <v>13.833333333333334</v>
+        <v>25.5</v>
       </c>
       <c r="AN4">
         <f>_xlfn.STDEV.P(AL4:AL46)</f>
-        <v>1.4337208778404378</v>
+        <v>0</v>
       </c>
       <c r="AP4">
         <f>1/3*(T4+Y4+AD4-3*AL4)</f>
-        <v>0.33333333333333331</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="AQ4">
         <f>AVERAGE(AP4:AP46)</f>
-        <v>1.8333333333333333</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="AR4">
         <f>_xlfn.STDEV.P(AP4:AP46)</f>
-        <v>2.1213203435596419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
@@ -1360,48 +1358,6 @@
       <c r="P5">
         <v>1.64134809501933</v>
       </c>
-      <c r="R5">
-        <v>22</v>
-      </c>
-      <c r="S5">
-        <v>7</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T6" si="0">AVERAGE(R5,S5)</f>
-        <v>14.5</v>
-      </c>
-      <c r="W5">
-        <v>19</v>
-      </c>
-      <c r="X5">
-        <v>9</v>
-      </c>
-      <c r="Y5">
-        <f t="shared" ref="Y5:Y6" si="1">AVERAGE(W5,X5)</f>
-        <v>14</v>
-      </c>
-      <c r="AB5">
-        <v>23</v>
-      </c>
-      <c r="AC5">
-        <v>6</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD6" si="2">AVERAGE(AB5,AC5)</f>
-        <v>14.5</v>
-      </c>
-      <c r="AH5">
-        <f t="shared" ref="AH5:AH6" si="3">AVERAGE(T5,Y5,AD5)</f>
-        <v>14.333333333333334</v>
-      </c>
-      <c r="AL5">
-        <f t="shared" ref="AL5:AL6" si="4">MIN(T5,Y5,AD5)</f>
-        <v>14</v>
-      </c>
-      <c r="AP5">
-        <f t="shared" ref="AP5:AP6" si="5">1/3*(T5+Y5+AD5-3*AL5)</f>
-        <v>0.33333333333333331</v>
-      </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
@@ -1437,48 +1393,6 @@
       <c r="P6">
         <v>2.08958657486883</v>
       </c>
-      <c r="R6">
-        <v>18</v>
-      </c>
-      <c r="S6">
-        <v>26</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="W6">
-        <v>18</v>
-      </c>
-      <c r="X6">
-        <v>13</v>
-      </c>
-      <c r="Y6">
-        <f t="shared" si="1"/>
-        <v>15.5</v>
-      </c>
-      <c r="AB6">
-        <v>23</v>
-      </c>
-      <c r="AC6">
-        <v>24</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="2"/>
-        <v>23.5</v>
-      </c>
-      <c r="AH6">
-        <f t="shared" si="3"/>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="AL6">
-        <f t="shared" si="4"/>
-        <v>15.5</v>
-      </c>
-      <c r="AP6">
-        <f t="shared" si="5"/>
-        <v>4.833333333333333</v>
-      </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
@@ -2969,6 +2883,36 @@
       <c r="D52" t="s">
         <v>50</v>
       </c>
+      <c r="E52">
+        <v>23.5</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>13.5</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>35</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>24</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>10.5</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
@@ -3149,6 +3093,36 @@
       <c r="D58" t="s">
         <v>62</v>
       </c>
+      <c r="E58">
+        <v>13.5</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>13.5</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>14</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>13.666666666666666</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C59">
@@ -3694,61 +3668,421 @@
       <c r="D77" t="s">
         <v>45</v>
       </c>
+      <c r="E77">
+        <v>19</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>21.5</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>20.5</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>20.333333333333332</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
         <v>46</v>
       </c>
+      <c r="E78">
+        <v>19.5</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>17</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>22.5</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>19.666666666666668</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>2.6666666666666701</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
         <v>47</v>
       </c>
+      <c r="E79">
+        <v>20</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>17</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>25</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>20.666666666666668</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
         <v>48</v>
       </c>
+      <c r="E80">
+        <v>20.5</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80">
+        <v>18</v>
+      </c>
+      <c r="H80">
+        <v>2.5</v>
+      </c>
+      <c r="I80">
+        <v>24.75</v>
+      </c>
+      <c r="J80">
+        <v>2.25</v>
+      </c>
+      <c r="K80">
+        <v>21.083333333333336</v>
+      </c>
+      <c r="L80">
+        <v>0.58333333333333393</v>
+      </c>
+      <c r="O80">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="P80">
+        <v>0.41666666666666696</v>
+      </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
         <v>49</v>
       </c>
+      <c r="E81">
+        <v>23.166666666666668</v>
+      </c>
+      <c r="F81">
+        <v>2.3921166824012206</v>
+      </c>
+      <c r="G81">
+        <v>21.666666666666668</v>
+      </c>
+      <c r="H81">
+        <v>2.0949675149960894</v>
+      </c>
+      <c r="I81">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="J81">
+        <v>4.4032816045409691</v>
+      </c>
+      <c r="K81">
+        <v>22.5</v>
+      </c>
+      <c r="L81">
+        <v>2.2484562605386738</v>
+      </c>
+      <c r="O81">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P81">
+        <v>1.0801234497346435</v>
+      </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
         <v>50</v>
       </c>
+      <c r="E82">
+        <v>28</v>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>19.25</v>
+      </c>
+      <c r="H82">
+        <v>0.25</v>
+      </c>
+      <c r="I82">
+        <v>23</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <v>23.416666666666664</v>
+      </c>
+      <c r="L82">
+        <v>1.5833333333333339</v>
+      </c>
+      <c r="O82">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="P82">
+        <v>1.8333333333333341</v>
+      </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
         <v>57</v>
       </c>
+      <c r="E83">
+        <v>21</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>20.5</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>20.5</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>20.666666666666668</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
         <v>58</v>
       </c>
+      <c r="E84">
+        <v>21</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>21</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>22.5</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>21.5</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0.5</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
         <v>59</v>
       </c>
+      <c r="E85">
+        <v>37</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>39.5</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>25</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>33.833333333333336</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
         <v>60</v>
       </c>
+      <c r="E86">
+        <v>28</v>
+      </c>
+      <c r="F86">
+        <v>1.5</v>
+      </c>
+      <c r="G86">
+        <v>29</v>
+      </c>
+      <c r="H86">
+        <v>3</v>
+      </c>
+      <c r="I86">
+        <v>24.75</v>
+      </c>
+      <c r="J86">
+        <v>2.25</v>
+      </c>
+      <c r="K86">
+        <v>27.25</v>
+      </c>
+      <c r="L86">
+        <v>0.75</v>
+      </c>
+      <c r="O86">
+        <v>3</v>
+      </c>
+      <c r="P86">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
         <v>61</v>
       </c>
+      <c r="E87">
+        <v>31.666666666666668</v>
+      </c>
+      <c r="F87">
+        <v>5.1370116691408141</v>
+      </c>
+      <c r="G87">
+        <v>28.333333333333332</v>
+      </c>
+      <c r="H87">
+        <v>3.39934634239519</v>
+      </c>
+      <c r="I87">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="J87">
+        <v>4.4032816045409691</v>
+      </c>
+      <c r="K87">
+        <v>27.555555555555557</v>
+      </c>
+      <c r="L87">
+        <v>3.381138678822857</v>
+      </c>
+      <c r="O87">
+        <v>4.8888888888888884</v>
+      </c>
+      <c r="P87">
+        <v>3.6675083209108901</v>
+      </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
         <v>62</v>
       </c>
+      <c r="E88">
+        <v>27.75</v>
+      </c>
+      <c r="F88">
+        <v>6.25</v>
+      </c>
+      <c r="G88">
+        <v>27.75</v>
+      </c>
+      <c r="H88">
+        <v>6.75</v>
+      </c>
+      <c r="I88">
+        <v>23</v>
+      </c>
+      <c r="J88">
+        <v>2</v>
+      </c>
+      <c r="K88">
+        <v>26.166666666666668</v>
+      </c>
+      <c r="L88">
+        <v>5.0000000000000115</v>
+      </c>
+      <c r="O88">
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="P88">
+        <v>2.9999999999999996</v>
+      </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C89">
@@ -4299,21 +4633,141 @@
       <c r="D108" t="s">
         <v>45</v>
       </c>
+      <c r="E108">
+        <v>12.5</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>19</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>29</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>20.166666666666668</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>7.6666666666666661</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
     </row>
     <row r="109" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
         <v>46</v>
       </c>
+      <c r="E109">
+        <v>41.5</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>28</v>
+      </c>
+      <c r="H109">
+        <v>22</v>
+      </c>
+      <c r="I109">
+        <v>13.5</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>34.5</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>21</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
     </row>
     <row r="110" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
         <v>47</v>
       </c>
+      <c r="E110">
+        <v>10</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>28</v>
+      </c>
+      <c r="H110">
+        <v>22</v>
+      </c>
+      <c r="I110">
+        <v>25</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>19.833333333333332</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>9.8333333333333321</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
     </row>
     <row r="111" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
         <v>48</v>
       </c>
+      <c r="E111">
+        <v>25.5</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>28</v>
+      </c>
+      <c r="H111">
+        <v>22</v>
+      </c>
+      <c r="I111">
+        <v>22</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>25.833333333333332</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>3.8333333333333299</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
     </row>
     <row r="112" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
@@ -4329,20 +4783,140 @@
       <c r="D114" t="s">
         <v>57</v>
       </c>
+      <c r="E114">
+        <v>12.5</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>13.5</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>13.5</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>13.166666666666666</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
     </row>
     <row r="115" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
         <v>58</v>
       </c>
+      <c r="E115">
+        <v>41.5</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>28</v>
+      </c>
+      <c r="H115">
+        <v>22</v>
+      </c>
+      <c r="I115">
+        <v>52.5</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>46.666666666666664</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>5.1666666666666661</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
     </row>
     <row r="116" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
         <v>59</v>
       </c>
+      <c r="E116">
+        <v>10</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>28</v>
+      </c>
+      <c r="H116">
+        <v>22</v>
+      </c>
+      <c r="I116">
+        <v>26.5</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>17.833333333333332</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
         <v>60</v>
+      </c>
+      <c r="E117">
+        <v>25.5</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>28</v>
+      </c>
+      <c r="H117">
+        <v>22</v>
+      </c>
+      <c r="I117">
+        <v>45</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>33.666666666666664</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>8.1666666666666661</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.3">

--- a/DataAnalysis/DataAnalysis.xlsx
+++ b/DataAnalysis/DataAnalysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63E8C7D-1A33-4E37-B489-AF459867001E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A9A717-FB68-4B97-91FF-3D7A6BF661FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{216728D3-2A76-4D61-AF39-758D90BA286A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{216728D3-2A76-4D61-AF39-758D90BA286A}"/>
   </bookViews>
   <sheets>
     <sheet name="DataAnalysis" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="55">
   <si>
     <t>DATASET</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t>STD_ERR</t>
-  </si>
-  <si>
-    <t>WERR</t>
-  </si>
-  <si>
-    <t>STD_WERR</t>
   </si>
   <si>
     <t>CIC</t>
@@ -205,24 +199,6 @@
   </si>
   <si>
     <t>TURKISH</t>
-  </si>
-  <si>
-    <t>MIT MAJ NOAUG</t>
-  </si>
-  <si>
-    <t>MIT MAJ PAR_BS</t>
-  </si>
-  <si>
-    <t>MIT MAJ STD_AUG</t>
-  </si>
-  <si>
-    <t>MIT MAJ DIFF ONLY MIN PAR_BS</t>
-  </si>
-  <si>
-    <t>MIT MAJ DIFF ONLY_MIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIT MAJ DIFF  </t>
   </si>
 </sst>
 </file>
@@ -365,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -545,6 +521,48 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -706,8 +724,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1083,32 +1109,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A698C200-6B38-4FC8-980C-FFCD18692E95}">
-  <dimension ref="A1:AR183"/>
+  <dimension ref="A1:AP183"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
-    <col min="13" max="13" width="6.21875" customWidth="1"/>
-    <col min="14" max="14" width="5.5546875" customWidth="1"/>
-    <col min="18" max="18" width="7.33203125" customWidth="1"/>
-    <col min="19" max="19" width="5.77734375" customWidth="1"/>
-    <col min="20" max="20" width="7" customWidth="1"/>
-    <col min="21" max="21" width="7.44140625" customWidth="1"/>
-    <col min="22" max="22" width="6.6640625" customWidth="1"/>
-    <col min="23" max="23" width="6.33203125" customWidth="1"/>
-    <col min="24" max="24" width="6.21875" customWidth="1"/>
-    <col min="26" max="26" width="8.109375" customWidth="1"/>
-    <col min="28" max="28" width="7.109375" customWidth="1"/>
-    <col min="29" max="29" width="6.6640625" customWidth="1"/>
-    <col min="30" max="30" width="6.77734375" customWidth="1"/>
-    <col min="31" max="31" width="7.109375" customWidth="1"/>
-    <col min="32" max="32" width="7" customWidth="1"/>
-    <col min="33" max="33" width="3.6640625" customWidth="1"/>
-    <col min="34" max="34" width="9.109375" customWidth="1"/>
-    <col min="37" max="37" width="3.109375" customWidth="1"/>
-    <col min="41" max="41" width="2.21875" customWidth="1"/>
+    <col min="6" max="6" width="2" customWidth="1"/>
+    <col min="8" max="8" width="2.44140625" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" customWidth="1"/>
+    <col min="12" max="12" width="1.6640625" customWidth="1"/>
+    <col min="14" max="14" width="2.109375" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
+    <col min="17" max="17" width="5.77734375" customWidth="1"/>
+    <col min="18" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="7.44140625" customWidth="1"/>
+    <col min="20" max="20" width="6.6640625" customWidth="1"/>
+    <col min="21" max="21" width="6.33203125" customWidth="1"/>
+    <col min="22" max="22" width="6.21875" customWidth="1"/>
+    <col min="24" max="24" width="8.109375" customWidth="1"/>
+    <col min="26" max="26" width="7.109375" customWidth="1"/>
+    <col min="27" max="27" width="6.6640625" customWidth="1"/>
+    <col min="28" max="28" width="6.77734375" customWidth="1"/>
+    <col min="29" max="29" width="7.109375" customWidth="1"/>
+    <col min="30" max="30" width="7" customWidth="1"/>
+    <col min="31" max="31" width="3.6640625" customWidth="1"/>
+    <col min="32" max="32" width="9.109375" customWidth="1"/>
+    <col min="35" max="35" width="3.109375" customWidth="1"/>
+    <col min="39" max="39" width="2.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1151,182 +1180,178 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="P3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="R3" t="s">
         <v>17</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" t="s">
         <v>18</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>19</v>
       </c>
-      <c r="U3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>20</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>23</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="s">
         <v>24</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AF3" t="s">
         <v>25</v>
       </c>
-      <c r="AE3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" t="s">
         <v>26</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AJ3" t="s">
         <v>27</v>
       </c>
-      <c r="AI3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>28</v>
       </c>
       <c r="AL3" t="s">
         <v>29</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AN3" t="s">
         <v>30</v>
       </c>
-      <c r="AN3" t="s">
-        <v>31</v>
+      <c r="AO3" t="s">
+        <v>12</v>
       </c>
       <c r="AP3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>0.05</v>
       </c>
+      <c r="P4">
+        <v>35</v>
+      </c>
+      <c r="Q4">
+        <v>11</v>
+      </c>
       <c r="R4">
-        <v>21</v>
+        <f>AVERAGE(P4:Q4)</f>
+        <v>23</v>
       </c>
       <c r="S4">
-        <v>30</v>
+        <f>AVERAGE(R4:R46)</f>
+        <v>23</v>
       </c>
       <c r="T4">
-        <f>AVERAGE(R4:S4)</f>
-        <v>25.5</v>
+        <f>_xlfn.STDEV.P(R4:R46)</f>
+        <v>0</v>
       </c>
       <c r="U4">
-        <f>AVERAGE(T4:T46)</f>
-        <v>25.5</v>
+        <v>15</v>
       </c>
       <c r="V4">
-        <f>_xlfn.STDEV.P(T4:T46)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>36</v>
+        <f>AVERAGE(U4:V4)</f>
+        <v>10.5</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <f>AVERAGE(W4:W81)</f>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <f>AVERAGE(W4:X4)</f>
-        <v>30.5</v>
+        <f>_xlfn.STDEV.P(W4:W41)</f>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AA4">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="AB4">
-        <v>51</v>
+        <f>AVERAGE(Z4:AA4)</f>
+        <v>43.5</v>
       </c>
       <c r="AC4">
-        <v>39</v>
+        <f>AVERAGE(AB4:AB46)</f>
+        <v>43.5</v>
       </c>
       <c r="AD4">
-        <f>AVERAGE(AB4:AC4)</f>
-        <v>45</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD46)</f>
-        <v>45</v>
+        <f>_xlfn.STDEV.P(AB4:AB46)</f>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <f>_xlfn.STDEV.P(AD4:AD46)</f>
-        <v>0</v>
+        <f>AVERAGE(R4,W4,AB4)</f>
+        <v>25.666666666666668</v>
+      </c>
+      <c r="AG4">
+        <f>AVERAGE(AF4:AF46)</f>
+        <v>25.666666666666668</v>
       </c>
       <c r="AH4">
-        <f>AVERAGE(T4,Y4,AD4)</f>
-        <v>33.666666666666664</v>
-      </c>
-      <c r="AI4">
-        <f>AVERAGE(AH4:AH46)</f>
-        <v>33.666666666666664</v>
+        <f>_xlfn.STDEV.P(AF4:AF46)</f>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <f>_xlfn.STDEV.P(AH4:AH46)</f>
-        <v>0</v>
+        <f>MIN(R4,W4,AB4)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AK4">
+        <f>AVERAGE(AJ4:AJ46)</f>
+        <v>10.5</v>
       </c>
       <c r="AL4">
-        <f>MIN(T4,Y4,AD4)</f>
-        <v>25.5</v>
-      </c>
-      <c r="AM4">
-        <f>AVERAGE(AL4:AL46)</f>
-        <v>25.5</v>
+        <f>_xlfn.STDEV.P(AJ4:AJ46)</f>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <f>_xlfn.STDEV.P(AL4:AL46)</f>
-        <v>0</v>
+        <f>1/3*(R4+W4+AB4-3*AJ4)</f>
+        <v>15.166666666666666</v>
+      </c>
+      <c r="AO4">
+        <f>AVERAGE(AN4:AN46)</f>
+        <v>15.166666666666666</v>
       </c>
       <c r="AP4">
-        <f>1/3*(T4+Y4+AD4-3*AL4)</f>
-        <v>8.1666666666666661</v>
-      </c>
-      <c r="AQ4">
-        <f>AVERAGE(AP4:AP46)</f>
-        <v>8.1666666666666661</v>
-      </c>
-      <c r="AR4">
-        <f>_xlfn.STDEV.P(AP4:AP46)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+        <f>_xlfn.STDEV.P(AN4:AN46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>15.075757575757599</v>
@@ -1352,16 +1377,16 @@
       <c r="L5">
         <v>2.1276473903136299</v>
       </c>
-      <c r="O5">
+      <c r="M5">
         <v>6.7979797979798002</v>
       </c>
-      <c r="P5">
+      <c r="N5">
         <v>1.64134809501933</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>15.34375</v>
@@ -1387,16 +1412,16 @@
       <c r="L6">
         <v>1.8925617885439801</v>
       </c>
-      <c r="O6">
+      <c r="M6">
         <v>6.2070707070707103</v>
       </c>
-      <c r="P6">
+      <c r="N6">
         <v>2.08958657486883</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>16.3333333333333</v>
@@ -1422,16 +1447,16 @@
       <c r="L7">
         <v>1.47064905466101</v>
       </c>
-      <c r="O7">
+      <c r="M7">
         <v>4.92592592592593</v>
       </c>
-      <c r="P7">
+      <c r="N7">
         <v>2.73113619914343</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>16.3333333333333</v>
@@ -1457,16 +1482,16 @@
       <c r="L8">
         <v>1.47064905466101</v>
       </c>
-      <c r="O8">
+      <c r="M8">
         <v>4.92592592592593</v>
       </c>
-      <c r="P8">
+      <c r="N8">
         <v>2.73113619914343</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>16.0833333333333</v>
@@ -1492,16 +1517,17 @@
       <c r="L9">
         <v>1.78081338053607</v>
       </c>
-      <c r="O9">
+      <c r="M9">
         <v>4.0555555555555598</v>
       </c>
-      <c r="P9">
+      <c r="N9">
         <v>1.5444044759016899</v>
       </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="O9" s="7"/>
+    </row>
+    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>14.4444444444444</v>
@@ -1527,16 +1553,16 @@
       <c r="L10">
         <v>1.3405476124459601</v>
       </c>
-      <c r="O10">
+      <c r="M10">
         <v>6.6481481481481497</v>
       </c>
-      <c r="P10">
+      <c r="N10">
         <v>2.2367580154663802</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>23</v>
@@ -1562,16 +1588,16 @@
       <c r="L11">
         <v>2.5927248643506702</v>
       </c>
-      <c r="O11">
+      <c r="M11">
         <v>8.5833333333333304</v>
       </c>
-      <c r="P11">
+      <c r="N11">
         <v>0.117851130197758</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>22.25</v>
@@ -1597,16 +1623,16 @@
       <c r="L12">
         <v>0.176776695296637</v>
       </c>
-      <c r="O12">
+      <c r="M12">
         <v>7.5833333333333304</v>
       </c>
-      <c r="P12">
+      <c r="N12">
         <v>0.35355339059327401</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>21.125</v>
@@ -1632,16 +1658,16 @@
       <c r="L13">
         <v>1.9917000810772101</v>
       </c>
-      <c r="O13">
+      <c r="M13">
         <v>7.21875</v>
       </c>
-      <c r="P13">
+      <c r="N13">
         <v>1.05484716726941</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14">
         <v>22.5</v>
@@ -1667,16 +1693,16 @@
       <c r="L14">
         <v>0.959665941427434</v>
       </c>
-      <c r="O14">
+      <c r="M14">
         <v>6.7118055555555598</v>
       </c>
-      <c r="P14">
+      <c r="N14">
         <v>1.89410279177305</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E15">
         <v>18</v>
@@ -1702,51 +1728,51 @@
       <c r="L15">
         <v>0.97657754618038595</v>
       </c>
-      <c r="O15">
+      <c r="M15">
         <v>4.7222222222222197</v>
       </c>
-      <c r="P15">
+      <c r="N15">
         <v>1.6694421334796401</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16">
         <v>14.5</v>
       </c>
-      <c r="F16" t="e">
-        <v>#DIV/0!</v>
+      <c r="F16">
+        <v>0</v>
       </c>
       <c r="G16">
         <v>12</v>
       </c>
-      <c r="H16" t="e">
-        <v>#DIV/0!</v>
+      <c r="H16">
+        <v>0</v>
       </c>
       <c r="I16">
         <v>24</v>
       </c>
-      <c r="J16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
         <v>16.8333333333333</v>
       </c>
-      <c r="L16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>4.8333333333333304</v>
       </c>
-      <c r="P16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E17">
         <v>15</v>
@@ -1772,16 +1798,16 @@
       <c r="L17">
         <v>0</v>
       </c>
-      <c r="O17">
+      <c r="M17">
         <v>6.333333333333333</v>
       </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="N17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>23</v>
@@ -1807,16 +1833,16 @@
       <c r="L18">
         <v>0</v>
       </c>
-      <c r="O18">
+      <c r="M18">
         <v>12.666666666666666</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="N18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E19">
         <v>16</v>
@@ -1842,16 +1868,17 @@
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="O19">
+      <c r="M19" s="1">
         <v>3.833333333333333</v>
       </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E20">
         <v>20</v>
@@ -1877,16 +1904,16 @@
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="O20">
+      <c r="M20">
         <v>9.5</v>
       </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="N20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E21">
         <v>17.25</v>
@@ -1912,16 +1939,16 @@
       <c r="L21">
         <v>0.33333333333333393</v>
       </c>
-      <c r="O21">
+      <c r="M21">
         <v>5.083333333333333</v>
       </c>
-      <c r="P21">
+      <c r="N21">
         <v>0.58333333333333404</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E22">
         <v>15.5</v>
@@ -1947,231 +1974,21 @@
       <c r="L22">
         <v>0</v>
       </c>
-      <c r="O22">
+      <c r="M22">
         <v>6.6666666666666661</v>
       </c>
-      <c r="P22">
+      <c r="N22">
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23">
-        <v>15</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>26.5</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>25.5</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>22.333333333333332</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>7.333333333333333</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24">
-        <v>23</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>31</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>33</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>29</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>6</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25">
-        <v>16</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>19</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>19.5</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>18.166666666666668</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>2.1666666666666665</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26">
-        <v>20</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>20</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>20</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>20</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27">
-        <v>17.25</v>
-      </c>
-      <c r="F27">
-        <v>0.25</v>
-      </c>
-      <c r="G27">
-        <v>17.125</v>
-      </c>
-      <c r="H27">
-        <v>0.125</v>
-      </c>
-      <c r="I27">
-        <v>17.25</v>
-      </c>
-      <c r="J27">
-        <v>0.25</v>
-      </c>
-      <c r="K27">
-        <v>17.208333333333336</v>
-      </c>
-      <c r="L27">
-        <v>0.20833333333333393</v>
-      </c>
-      <c r="O27">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="P27">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28">
-        <v>15.5</v>
-      </c>
-      <c r="F28">
-        <v>0.5</v>
-      </c>
-      <c r="G28">
-        <v>15.5</v>
-      </c>
-      <c r="H28">
-        <v>0.5</v>
-      </c>
-      <c r="I28">
-        <v>15.5</v>
-      </c>
-      <c r="J28">
-        <v>0.5</v>
-      </c>
-      <c r="K28">
-        <v>15.5</v>
-      </c>
-      <c r="L28">
-        <v>0.5</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C29">
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E30">
         <v>18</v>
@@ -2197,16 +2014,16 @@
       <c r="L30">
         <v>0</v>
       </c>
-      <c r="O30">
+      <c r="M30">
         <v>4.333333333333333</v>
       </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="N30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E31">
         <v>17.125</v>
@@ -2226,22 +2043,23 @@
       <c r="J31">
         <v>1.625</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>20</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
-      <c r="O31">
+      <c r="M31" s="1">
         <v>4.25</v>
       </c>
-      <c r="P31">
+      <c r="N31">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="O31" s="8"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E32">
         <v>13.25</v>
@@ -2267,26 +2085,26 @@
       <c r="L32">
         <v>1.3333333333333339</v>
       </c>
-      <c r="O32">
+      <c r="M32">
         <v>6.9166666666666661</v>
       </c>
-      <c r="P32">
+      <c r="N32">
         <v>0.58333333333333348</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C34">
         <v>0.05</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E35">
         <v>22.515625</v>
@@ -2312,16 +2130,16 @@
       <c r="L35">
         <v>0.5</v>
       </c>
-      <c r="O35">
+      <c r="M35">
         <v>11.5</v>
       </c>
-      <c r="P35">
+      <c r="N35">
         <v>0.28867513459481298</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E36">
         <v>25.0625</v>
@@ -2347,16 +2165,16 @@
       <c r="L36">
         <v>2.0094299296007598</v>
       </c>
-      <c r="O36">
+      <c r="M36">
         <v>12.6041666666667</v>
       </c>
-      <c r="P36">
+      <c r="N36">
         <v>1.9536520346268</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E37">
         <v>22.4166666666667</v>
@@ -2376,22 +2194,23 @@
       <c r="J37">
         <v>4.3011626335213098</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="2">
         <v>21.5277777777778</v>
       </c>
       <c r="L37">
         <v>0.99675399097195505</v>
       </c>
-      <c r="O37">
+      <c r="M37" s="2">
         <v>8.8611111111111107</v>
       </c>
-      <c r="P37">
+      <c r="N37">
         <v>2.89907392620982</v>
       </c>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O37" s="7"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E38">
         <v>23.8888888888889</v>
@@ -2411,22 +2230,22 @@
       <c r="J38">
         <v>4.0474614815269598</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="1">
         <v>22.4444444444444</v>
       </c>
       <c r="L38">
         <v>1.8837757592428901</v>
       </c>
-      <c r="O38">
+      <c r="M38">
         <v>10.7222222222222</v>
       </c>
-      <c r="P38">
+      <c r="N38">
         <v>2.50138850330061</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>24.1666666666667</v>
@@ -2452,16 +2271,16 @@
       <c r="L39">
         <v>1.8036314534164399</v>
       </c>
-      <c r="O39">
+      <c r="M39">
         <v>9.3148148148148202</v>
       </c>
-      <c r="P39">
+      <c r="N39">
         <v>2.53783104633722</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E40">
         <v>24.1666666666667</v>
@@ -2487,16 +2306,17 @@
       <c r="L40">
         <v>1.8036314534164399</v>
       </c>
-      <c r="O40">
+      <c r="M40" s="1">
         <v>9.3148148148148202</v>
       </c>
-      <c r="P40">
+      <c r="N40">
         <v>2.53783104633722</v>
       </c>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O40" s="8"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>30.1428571428571</v>
@@ -2522,16 +2342,16 @@
       <c r="L41">
         <v>3.7921535823179799</v>
       </c>
-      <c r="O41">
+      <c r="M41">
         <v>10.8611111111111</v>
       </c>
-      <c r="P41">
+      <c r="N41">
         <v>4.03332950719133</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E42">
         <v>24.625</v>
@@ -2557,16 +2377,16 @@
       <c r="L42">
         <v>2.2128709495824999</v>
       </c>
-      <c r="O42">
+      <c r="M42">
         <v>9.9444444444444393</v>
       </c>
-      <c r="P42">
+      <c r="N42">
         <v>1.71233722304694</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E43">
         <v>23.285714285714299</v>
@@ -2592,16 +2412,16 @@
       <c r="L43">
         <v>1.4782092251192001</v>
       </c>
-      <c r="O43">
+      <c r="M43">
         <v>11.8333333333333</v>
       </c>
-      <c r="P43">
+      <c r="N43">
         <v>1.93708926351235</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E44">
         <v>24.714285714285701</v>
@@ -2627,16 +2447,16 @@
       <c r="L44">
         <v>2.0136562536680702</v>
       </c>
-      <c r="O44">
+      <c r="M44">
         <v>11.3174603174603</v>
       </c>
-      <c r="P44">
+      <c r="N44">
         <v>1.58145251698939</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E45">
         <v>25</v>
@@ -2662,16 +2482,16 @@
       <c r="L45">
         <v>2.8349668493717899</v>
       </c>
-      <c r="O45">
+      <c r="M45">
         <v>12.7222222222222</v>
       </c>
-      <c r="P45">
+      <c r="N45">
         <v>5.0726207705170996</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E46">
         <v>23.428571428571399</v>
@@ -2697,16 +2517,16 @@
       <c r="L46">
         <v>1.1575608363913701</v>
       </c>
-      <c r="O46">
+      <c r="M46">
         <v>9.3571428571428594</v>
       </c>
-      <c r="P46">
+      <c r="N46">
         <v>2.88101797118042</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E47">
         <v>26.5</v>
@@ -2732,16 +2552,16 @@
       <c r="L47">
         <v>0</v>
       </c>
-      <c r="O47">
+      <c r="M47">
         <v>11.6666666666667</v>
       </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E48">
         <v>45.5</v>
@@ -2767,16 +2587,16 @@
       <c r="L48">
         <v>0</v>
       </c>
-      <c r="O48">
+      <c r="M48">
         <v>13</v>
       </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E49">
         <v>30</v>
@@ -2802,16 +2622,16 @@
       <c r="L49">
         <v>0</v>
       </c>
-      <c r="O49">
+      <c r="M49">
         <v>13.5</v>
       </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E50">
         <v>31.5</v>
@@ -2837,16 +2657,16 @@
       <c r="L50">
         <v>0</v>
       </c>
-      <c r="O50">
+      <c r="M50">
         <v>12.5</v>
       </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E51">
         <v>26</v>
@@ -2872,16 +2692,16 @@
       <c r="L51">
         <v>1.2196943555611197</v>
       </c>
-      <c r="O51">
+      <c r="M51">
         <v>11.722222222222221</v>
       </c>
-      <c r="P51">
+      <c r="N51">
         <v>0.69832250499869608</v>
       </c>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E52">
         <v>23.5</v>
@@ -2907,231 +2727,21 @@
       <c r="L52">
         <v>0</v>
       </c>
-      <c r="O52">
+      <c r="M52">
         <v>10.5</v>
       </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D53" t="s">
-        <v>57</v>
-      </c>
-      <c r="E53">
-        <v>16</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>13.5</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>24.5</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>18</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>4.5</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D54" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54">
-        <v>48.5</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>26.5</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>32</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>35.666666666666664</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>9.1666666666666696</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D55" t="s">
-        <v>59</v>
-      </c>
-      <c r="E55">
-        <v>30.5</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>15.5</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>37</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>27.666666666666668</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>12.166666666666666</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D56" t="s">
-        <v>60</v>
-      </c>
-      <c r="E56">
-        <v>23</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>18</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>36.5</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>25.833333333333332</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>7.833333333333333</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D57" t="s">
-        <v>61</v>
-      </c>
-      <c r="E57">
-        <v>16.166666666666668</v>
-      </c>
-      <c r="F57">
-        <v>4.2491829279939877</v>
-      </c>
-      <c r="G57">
-        <v>14</v>
-      </c>
-      <c r="H57">
-        <v>1.2247448713915889</v>
-      </c>
-      <c r="I57">
-        <v>16.833333333333332</v>
-      </c>
-      <c r="J57">
-        <v>4.7842333648024411</v>
-      </c>
-      <c r="K57">
-        <v>15.666666666666666</v>
-      </c>
-      <c r="L57">
-        <v>3.39934634239519</v>
-      </c>
-      <c r="O57">
-        <v>1.8333333333333333</v>
-      </c>
-      <c r="P57">
-        <v>2.1213203435596419</v>
-      </c>
-    </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D58" t="s">
-        <v>62</v>
-      </c>
-      <c r="E58">
-        <v>13.5</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>13.5</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>14</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>13.666666666666666</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C59">
         <v>0.2</v>
       </c>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E60">
         <v>26</v>
@@ -3157,16 +2767,16 @@
       <c r="L60">
         <v>0</v>
       </c>
-      <c r="O60">
+      <c r="M60">
         <v>12.833333333333332</v>
       </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E61">
         <v>22</v>
@@ -3186,22 +2796,22 @@
       <c r="J61">
         <v>0</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="1">
         <v>22.166666666666668</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
-      <c r="O61">
+      <c r="M61">
         <v>10.166666666666666</v>
       </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E62">
         <v>22</v>
@@ -3227,26 +2837,27 @@
       <c r="L62">
         <v>0</v>
       </c>
-      <c r="O62">
+      <c r="M62" s="1">
         <v>8.1666666666666661</v>
       </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62" s="8"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C64">
         <v>0.05</v>
       </c>
     </row>
-    <row r="65" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E65">
         <v>20.806451612903199</v>
@@ -3272,16 +2883,16 @@
       <c r="L65">
         <v>1.75352378912074</v>
       </c>
-      <c r="O65">
+      <c r="M65">
         <v>3.3494623655914002</v>
       </c>
-      <c r="P65">
+      <c r="N65">
         <v>1.97922302315537</v>
       </c>
     </row>
-    <row r="66" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E66">
         <v>23.4838709677419</v>
@@ -3307,16 +2918,16 @@
       <c r="L66">
         <v>1.2184284555256299</v>
       </c>
-      <c r="O66">
+      <c r="M66">
         <v>2.9032258064516099</v>
       </c>
-      <c r="P66">
+      <c r="N66">
         <v>1.78873749888138</v>
       </c>
     </row>
-    <row r="67" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E67">
         <v>21.1666666666667</v>
@@ -3336,22 +2947,23 @@
       <c r="J67">
         <v>2.69567554922076</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="2">
         <v>18.3333333333333</v>
       </c>
       <c r="L67">
         <v>2.4289915602982202</v>
       </c>
-      <c r="O67">
+      <c r="M67">
         <v>3.1666666666666701</v>
       </c>
-      <c r="P67">
+      <c r="N67">
         <v>1.0801234497346399</v>
       </c>
-    </row>
-    <row r="68" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="O67" s="7"/>
+    </row>
+    <row r="68" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E68">
         <v>21.7222222222222</v>
@@ -3377,16 +2989,16 @@
       <c r="L68">
         <v>1.5163715626618</v>
       </c>
-      <c r="O68">
+      <c r="M68">
         <v>3.3703703703703698</v>
       </c>
-      <c r="P68">
+      <c r="N68">
         <v>1.95394504389655</v>
       </c>
     </row>
-    <row r="69" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E69">
         <v>23.285714285714299</v>
@@ -3412,16 +3024,16 @@
       <c r="L69">
         <v>2.53285292019571</v>
       </c>
-      <c r="O69">
+      <c r="M69">
         <v>3.5</v>
       </c>
-      <c r="P69">
+      <c r="N69">
         <v>0.96704973252940096</v>
       </c>
     </row>
-    <row r="70" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E70">
         <v>23.8888888888889</v>
@@ -3447,16 +3059,16 @@
       <c r="L70">
         <v>2.4225662344905698</v>
       </c>
-      <c r="O70">
+      <c r="M70">
         <v>3.9629629629629601</v>
       </c>
-      <c r="P70">
+      <c r="N70">
         <v>1.7594541802347901</v>
       </c>
     </row>
-    <row r="71" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E71">
         <v>28.3571428571429</v>
@@ -3482,16 +3094,16 @@
       <c r="L71">
         <v>5.0615915475973603</v>
       </c>
-      <c r="O71">
+      <c r="M71">
         <v>8.6111111111111107</v>
       </c>
-      <c r="P71">
+      <c r="N71">
         <v>3.29667340747541</v>
       </c>
     </row>
-    <row r="72" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E72">
         <v>25.071428571428601</v>
@@ -3517,16 +3129,16 @@
       <c r="L72">
         <v>3.53831930204796</v>
       </c>
-      <c r="O72">
+      <c r="M72">
         <v>8.4682539682539701</v>
       </c>
-      <c r="P72">
+      <c r="N72">
         <v>2.5567845561004798</v>
       </c>
     </row>
-    <row r="73" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E73">
         <v>23.1428571428571</v>
@@ -3552,16 +3164,16 @@
       <c r="L73">
         <v>2.6211233657370498</v>
       </c>
-      <c r="O73">
+      <c r="M73">
         <v>5.9682539682539701</v>
       </c>
-      <c r="P73">
+      <c r="N73">
         <v>1.05925625300199</v>
       </c>
     </row>
-    <row r="74" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E74">
         <v>25.1428571428571</v>
@@ -3587,16 +3199,16 @@
       <c r="L74">
         <v>2.3672015287257202</v>
       </c>
-      <c r="O74">
+      <c r="M74">
         <v>4.5337301587301599</v>
       </c>
-      <c r="P74">
+      <c r="N74">
         <v>1.7422273217248001</v>
       </c>
     </row>
-    <row r="75" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E75">
         <v>25.6666666666667</v>
@@ -3622,16 +3234,16 @@
       <c r="L75">
         <v>2.6666666666666701</v>
       </c>
-      <c r="O75">
+      <c r="M75">
         <v>4.5</v>
       </c>
-      <c r="P75">
+      <c r="N75">
         <v>2.6822461565718498</v>
       </c>
     </row>
-    <row r="76" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E76">
         <v>22.0833333333333</v>
@@ -3651,22 +3263,22 @@
       <c r="J76">
         <v>2.8240042492885902</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="1">
         <v>19.1388888888889</v>
       </c>
       <c r="L76">
         <v>1.41192015302513</v>
       </c>
-      <c r="O76">
+      <c r="M76">
         <v>3.2222222222222201</v>
       </c>
-      <c r="P76">
+      <c r="N76">
         <v>1.9682667690316</v>
       </c>
     </row>
-    <row r="77" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E77">
         <v>19</v>
@@ -3692,16 +3304,17 @@
       <c r="L77">
         <v>0</v>
       </c>
-      <c r="O77">
+      <c r="M77" s="1">
         <v>1.3333333333333299</v>
       </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" s="8"/>
+    </row>
+    <row r="78" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E78">
         <v>19.5</v>
@@ -3727,16 +3340,16 @@
       <c r="L78">
         <v>0</v>
       </c>
-      <c r="O78">
+      <c r="M78">
         <v>2.6666666666666701</v>
       </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E79">
         <v>20</v>
@@ -3762,16 +3375,16 @@
       <c r="L79">
         <v>0</v>
       </c>
-      <c r="O79">
+      <c r="M79">
         <v>3.6666666666666665</v>
       </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E80">
         <v>20.5</v>
@@ -3797,16 +3410,16 @@
       <c r="L80">
         <v>0.58333333333333393</v>
       </c>
-      <c r="O80">
+      <c r="M80">
         <v>4.583333333333333</v>
       </c>
-      <c r="P80">
+      <c r="N80">
         <v>0.41666666666666696</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E81">
         <v>23.166666666666668</v>
@@ -3832,16 +3445,16 @@
       <c r="L81">
         <v>2.2484562605386738</v>
       </c>
-      <c r="O81">
+      <c r="M81">
         <v>2.333333333333333</v>
       </c>
-      <c r="P81">
+      <c r="N81">
         <v>1.0801234497346435</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E82">
         <v>28</v>
@@ -3867,231 +3480,21 @@
       <c r="L82">
         <v>1.5833333333333339</v>
       </c>
-      <c r="O82">
+      <c r="M82">
         <v>4.1666666666666661</v>
       </c>
-      <c r="P82">
+      <c r="N82">
         <v>1.8333333333333341</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D83" t="s">
-        <v>57</v>
-      </c>
-      <c r="E83">
-        <v>21</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-      <c r="G83">
-        <v>20.5</v>
-      </c>
-      <c r="H83">
-        <v>0</v>
-      </c>
-      <c r="I83">
-        <v>20.5</v>
-      </c>
-      <c r="J83">
-        <v>0</v>
-      </c>
-      <c r="K83">
-        <v>20.666666666666668</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D84" t="s">
-        <v>58</v>
-      </c>
-      <c r="E84">
-        <v>21</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <v>21</v>
-      </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-      <c r="I84">
-        <v>22.5</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84">
-        <v>21.5</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0.5</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D85" t="s">
-        <v>59</v>
-      </c>
-      <c r="E85">
-        <v>37</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="G85">
-        <v>39.5</v>
-      </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-      <c r="I85">
-        <v>25</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <v>33.833333333333336</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>8.8333333333333321</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D86" t="s">
-        <v>60</v>
-      </c>
-      <c r="E86">
-        <v>28</v>
-      </c>
-      <c r="F86">
-        <v>1.5</v>
-      </c>
-      <c r="G86">
-        <v>29</v>
-      </c>
-      <c r="H86">
-        <v>3</v>
-      </c>
-      <c r="I86">
-        <v>24.75</v>
-      </c>
-      <c r="J86">
-        <v>2.25</v>
-      </c>
-      <c r="K86">
-        <v>27.25</v>
-      </c>
-      <c r="L86">
-        <v>0.75</v>
-      </c>
-      <c r="O86">
-        <v>3</v>
-      </c>
-      <c r="P86">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D87" t="s">
-        <v>61</v>
-      </c>
-      <c r="E87">
-        <v>31.666666666666668</v>
-      </c>
-      <c r="F87">
-        <v>5.1370116691408141</v>
-      </c>
-      <c r="G87">
-        <v>28.333333333333332</v>
-      </c>
-      <c r="H87">
-        <v>3.39934634239519</v>
-      </c>
-      <c r="I87">
-        <v>22.666666666666668</v>
-      </c>
-      <c r="J87">
-        <v>4.4032816045409691</v>
-      </c>
-      <c r="K87">
-        <v>27.555555555555557</v>
-      </c>
-      <c r="L87">
-        <v>3.381138678822857</v>
-      </c>
-      <c r="O87">
-        <v>4.8888888888888884</v>
-      </c>
-      <c r="P87">
-        <v>3.6675083209108901</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D88" t="s">
-        <v>62</v>
-      </c>
-      <c r="E88">
-        <v>27.75</v>
-      </c>
-      <c r="F88">
-        <v>6.25</v>
-      </c>
-      <c r="G88">
-        <v>27.75</v>
-      </c>
-      <c r="H88">
-        <v>6.75</v>
-      </c>
-      <c r="I88">
-        <v>23</v>
-      </c>
-      <c r="J88">
-        <v>2</v>
-      </c>
-      <c r="K88">
-        <v>26.166666666666668</v>
-      </c>
-      <c r="L88">
-        <v>5.0000000000000115</v>
-      </c>
-      <c r="O88">
-        <v>3.1666666666666665</v>
-      </c>
-      <c r="P88">
-        <v>2.9999999999999996</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C89">
         <v>0.2</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E90">
         <v>25.5</v>
@@ -4117,16 +3520,16 @@
       <c r="L90">
         <v>0</v>
       </c>
-      <c r="O90">
+      <c r="M90">
         <v>4.833333333333333</v>
       </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E91">
         <v>20</v>
@@ -4146,22 +3549,23 @@
       <c r="J91">
         <v>0</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="1">
         <v>18</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
-      <c r="O91">
+      <c r="M91" s="1">
         <v>3.5</v>
       </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91" s="8"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E92">
         <v>18</v>
@@ -4187,31 +3591,31 @@
       <c r="L92">
         <v>0</v>
       </c>
-      <c r="O92">
+      <c r="M92">
         <v>5.333333333333333</v>
       </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C95">
         <v>0.05</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E96">
         <v>10.346153846153801</v>
@@ -4237,16 +3641,16 @@
       <c r="L96">
         <v>1.89317324570986</v>
       </c>
-      <c r="O96">
+      <c r="M96">
         <v>5.0833333333333304</v>
       </c>
-      <c r="P96">
+      <c r="N96">
         <v>2.3681919967209901</v>
       </c>
     </row>
-    <row r="97" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E97">
         <v>11.846153846153801</v>
@@ -4272,16 +3676,16 @@
       <c r="L97">
         <v>2.0840739424336299</v>
       </c>
-      <c r="O97">
+      <c r="M97">
         <v>7.9102564102564097</v>
       </c>
-      <c r="P97">
+      <c r="N97">
         <v>1.63244786743284</v>
       </c>
     </row>
-    <row r="98" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E98">
         <v>11</v>
@@ -4301,22 +3705,23 @@
       <c r="J98">
         <v>2.8431203515386598</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="2">
         <v>14.3888888888889</v>
       </c>
       <c r="L98">
         <v>0.41943524640393098</v>
       </c>
-      <c r="O98">
+      <c r="M98" s="4">
         <v>3.3888888888888902</v>
       </c>
-      <c r="P98">
+      <c r="N98">
         <v>0.91792842454768298</v>
       </c>
-    </row>
-    <row r="99" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="O98" s="7"/>
+    </row>
+    <row r="99" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E99">
         <v>10</v>
@@ -4342,16 +3747,16 @@
       <c r="L99">
         <v>2.1424933553637402</v>
       </c>
-      <c r="O99">
+      <c r="M99">
         <v>5.3333333333333304</v>
       </c>
-      <c r="P99">
+      <c r="N99">
         <v>1.3869430814244399</v>
       </c>
     </row>
-    <row r="100" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E100">
         <v>10.6666666666667</v>
@@ -4377,16 +3782,16 @@
       <c r="L100">
         <v>2.0838888148345598</v>
       </c>
-      <c r="O100">
+      <c r="M100">
         <v>5.7777777777777803</v>
       </c>
-      <c r="P100">
+      <c r="N100">
         <v>2.39405126960169</v>
       </c>
     </row>
-    <row r="101" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E101">
         <v>8.6875</v>
@@ -4412,16 +3817,16 @@
       <c r="L101">
         <v>1.74446403284928</v>
       </c>
-      <c r="O101">
+      <c r="M101">
         <v>9.3333333333333304</v>
       </c>
-      <c r="P101">
+      <c r="N101">
         <v>1.79284291400159</v>
       </c>
     </row>
-    <row r="102" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E102">
         <v>23.25</v>
@@ -4447,16 +3852,16 @@
       <c r="L102">
         <v>3.53553390593274</v>
       </c>
-      <c r="O102">
+      <c r="M102">
         <v>3</v>
       </c>
-      <c r="P102">
+      <c r="N102">
         <v>1.4142135623731</v>
       </c>
     </row>
-    <row r="103" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E103">
         <v>22</v>
@@ -4482,16 +3887,16 @@
       <c r="L103">
         <v>3.1666666666666745</v>
       </c>
-      <c r="O103">
+      <c r="M103" s="3">
         <v>2.25</v>
       </c>
-      <c r="P103">
+      <c r="N103">
         <v>0.91666666666666607</v>
       </c>
     </row>
-    <row r="104" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E104">
         <v>16.5625</v>
@@ -4517,16 +3922,16 @@
       <c r="L104">
         <v>1.3266433729110811</v>
       </c>
-      <c r="O104">
+      <c r="M104">
         <v>5.145833333333333</v>
       </c>
-      <c r="P104">
+      <c r="N104">
         <v>1.2786643965047628</v>
       </c>
     </row>
-    <row r="105" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E105">
         <v>15.893790832183692</v>
@@ -4552,51 +3957,52 @@
       <c r="L105">
         <v>0.12818695514442738</v>
       </c>
-      <c r="O105">
+      <c r="M105">
         <v>4.7539148351648342</v>
       </c>
-      <c r="P105">
+      <c r="N105">
         <v>0.1372248076908337</v>
       </c>
     </row>
-    <row r="106" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E106">
         <v>10.5</v>
       </c>
-      <c r="F106" t="e">
-        <v>#DIV/0!</v>
+      <c r="F106">
+        <v>0</v>
       </c>
       <c r="G106">
         <v>12</v>
       </c>
-      <c r="H106" t="e">
-        <v>#DIV/0!</v>
+      <c r="H106">
+        <v>0</v>
       </c>
       <c r="I106">
         <v>21.5</v>
       </c>
-      <c r="J106" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K106">
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106" s="1">
         <v>14.6666666666667</v>
       </c>
-      <c r="L106" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O106">
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106" s="1">
         <v>4.1666666666666696</v>
       </c>
-      <c r="P106" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="107" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106" s="8"/>
+    </row>
+    <row r="107" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E107">
         <v>8.5833333333333304</v>
@@ -4622,16 +4028,16 @@
       <c r="L107">
         <v>1.33749350984926</v>
       </c>
-      <c r="O107">
+      <c r="M107">
         <v>7.4166666666666696</v>
       </c>
-      <c r="P107">
+      <c r="N107">
         <v>1.1820415484331399</v>
       </c>
     </row>
-    <row r="108" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E108">
         <v>12.5</v>
@@ -4657,16 +4063,16 @@
       <c r="L108">
         <v>0</v>
       </c>
-      <c r="O108">
+      <c r="M108">
         <v>7.6666666666666661</v>
       </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E109">
         <v>41.5</v>
@@ -4675,33 +4081,33 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>28</v>
+        <v>48.5</v>
       </c>
       <c r="H109">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I109">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109">
-        <v>34.5</v>
+        <v>38.333333333333336</v>
       </c>
       <c r="L109">
         <v>0</v>
       </c>
-      <c r="O109">
-        <v>21</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="M109">
+        <v>13.333333333333332</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E110">
         <v>10</v>
@@ -4710,10 +4116,10 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>28</v>
+        <v>24.5</v>
       </c>
       <c r="H110">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I110">
         <v>25</v>
@@ -4727,16 +4133,16 @@
       <c r="L110">
         <v>0</v>
       </c>
-      <c r="O110">
+      <c r="M110">
         <v>9.8333333333333321</v>
       </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E111">
         <v>25.5</v>
@@ -4745,10 +4151,10 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H111">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I111">
         <v>22</v>
@@ -4762,181 +4168,91 @@
       <c r="L111">
         <v>0</v>
       </c>
-      <c r="O111">
-        <v>3.8333333333333299</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="M111">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="E112">
+        <v>15.5</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>27</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>27</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>23.166666666666668</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>7.6666666666666661</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D114" t="s">
-        <v>57</v>
-      </c>
-      <c r="E114">
-        <v>12.5</v>
-      </c>
-      <c r="F114">
-        <v>0</v>
-      </c>
-      <c r="G114">
-        <v>13.5</v>
-      </c>
-      <c r="H114">
-        <v>0</v>
-      </c>
-      <c r="I114">
-        <v>13.5</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>13.166666666666666</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D115" t="s">
-        <v>58</v>
-      </c>
-      <c r="E115">
-        <v>41.5</v>
-      </c>
-      <c r="F115">
-        <v>0</v>
-      </c>
-      <c r="G115">
-        <v>28</v>
-      </c>
-      <c r="H115">
-        <v>22</v>
-      </c>
-      <c r="I115">
-        <v>52.5</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <v>46.666666666666664</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>5.1666666666666661</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D116" t="s">
-        <v>59</v>
-      </c>
-      <c r="E116">
-        <v>10</v>
-      </c>
-      <c r="F116">
-        <v>0</v>
-      </c>
-      <c r="G116">
-        <v>28</v>
-      </c>
-      <c r="H116">
-        <v>22</v>
-      </c>
-      <c r="I116">
-        <v>26.5</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>17.833333333333332</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>7.833333333333333</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D117" t="s">
-        <v>60</v>
-      </c>
-      <c r="E117">
-        <v>25.5</v>
-      </c>
-      <c r="F117">
-        <v>0</v>
-      </c>
-      <c r="G117">
-        <v>28</v>
-      </c>
-      <c r="H117">
-        <v>22</v>
-      </c>
-      <c r="I117">
-        <v>45</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>33.666666666666664</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>8.1666666666666661</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D118" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="119" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D119" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="120" spans="2:16" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="E113">
+        <v>10.75</v>
+      </c>
+      <c r="F113">
+        <v>0.75</v>
+      </c>
+      <c r="G113">
+        <v>18</v>
+      </c>
+      <c r="H113">
+        <v>1.5</v>
+      </c>
+      <c r="I113">
+        <v>20.75</v>
+      </c>
+      <c r="J113">
+        <v>0.25</v>
+      </c>
+      <c r="K113">
+        <v>16.5</v>
+      </c>
+      <c r="L113">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="M113">
+        <v>5.75</v>
+      </c>
+      <c r="N113">
+        <v>8.3333333333333481E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C120">
         <v>0.2</v>
       </c>
     </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E121">
         <v>13.5</v>
@@ -4956,22 +4272,23 @@
       <c r="J121">
         <v>0</v>
       </c>
-      <c r="K121">
+      <c r="K121" s="1">
         <v>13.5</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
-      <c r="O121">
+      <c r="M121">
         <v>2</v>
       </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121" s="8"/>
+    </row>
+    <row r="122" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E122">
         <v>10</v>
@@ -4997,16 +4314,16 @@
       <c r="L122">
         <v>0</v>
       </c>
-      <c r="O122">
+      <c r="M122">
         <v>5</v>
       </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E123">
         <v>17</v>
@@ -5032,26 +4349,26 @@
       <c r="L123">
         <v>0</v>
       </c>
-      <c r="O123">
+      <c r="M123" s="1">
         <v>1.6666666666666665</v>
       </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="125" spans="2:16" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="125" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C125">
         <v>0.05</v>
       </c>
     </row>
-    <row r="126" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E126">
         <v>18.384615384615401</v>
@@ -5077,16 +4394,16 @@
       <c r="L126">
         <v>1.67866054774868</v>
       </c>
-      <c r="O126">
+      <c r="M126">
         <v>7.7692307692307701</v>
       </c>
-      <c r="P126">
+      <c r="N126">
         <v>2.34376483850953</v>
       </c>
     </row>
-    <row r="127" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E127">
         <v>19.038461538461501</v>
@@ -5112,16 +4429,16 @@
       <c r="L127">
         <v>1.00730357580382</v>
       </c>
-      <c r="O127">
+      <c r="M127">
         <v>10.2692307692308</v>
       </c>
-      <c r="P127">
+      <c r="N127">
         <v>2.0282021567398001</v>
       </c>
     </row>
-    <row r="128" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E128">
         <v>14.3333333333333</v>
@@ -5141,22 +4458,23 @@
       <c r="J128">
         <v>5.26782687642637</v>
       </c>
-      <c r="K128">
+      <c r="K128" s="4">
         <v>14.4444444444444</v>
       </c>
       <c r="L128">
         <v>0.85526690657448001</v>
       </c>
-      <c r="O128">
+      <c r="M128" s="5">
         <v>5.4444444444444402</v>
       </c>
-      <c r="P128">
+      <c r="N128">
         <v>1.75066125073208</v>
       </c>
-    </row>
-    <row r="129" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="O128" s="7"/>
+    </row>
+    <row r="129" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E129">
         <v>16.0555555555556</v>
@@ -5176,22 +4494,23 @@
       <c r="J129">
         <v>5.87957859412088</v>
       </c>
-      <c r="K129">
+      <c r="K129" s="1">
         <v>17.592592592592599</v>
       </c>
       <c r="L129">
         <v>2.3660079938919201</v>
       </c>
-      <c r="O129">
+      <c r="M129">
         <v>7.4814814814814801</v>
       </c>
-      <c r="P129">
+      <c r="N129">
         <v>3.4221951658382102</v>
       </c>
-    </row>
-    <row r="130" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="O129" s="8"/>
+    </row>
+    <row r="130" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E130">
         <v>17.2222222222222</v>
@@ -5217,16 +4536,16 @@
       <c r="L130">
         <v>2.16470709106878</v>
       </c>
-      <c r="O130">
+      <c r="M130">
         <v>8.9629629629629601</v>
       </c>
-      <c r="P130">
+      <c r="N130">
         <v>1.66620363938543</v>
       </c>
     </row>
-    <row r="131" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E131">
         <v>17.2222222222222</v>
@@ -5252,16 +4571,16 @@
       <c r="L131">
         <v>2.16470709106878</v>
       </c>
-      <c r="O131">
+      <c r="M131">
         <v>8.9629629629629601</v>
       </c>
-      <c r="P131">
+      <c r="N131">
         <v>1.66620363938543</v>
       </c>
     </row>
-    <row r="132" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E132">
         <v>29.5</v>
@@ -5287,16 +4606,16 @@
       <c r="L132">
         <v>1.8333333333333339</v>
       </c>
-      <c r="O132">
+      <c r="M132" s="3">
         <v>6.333333333333333</v>
       </c>
-      <c r="P132">
+      <c r="N132">
         <v>0.66666666666667085</v>
       </c>
     </row>
-    <row r="133" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="133" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E133">
         <v>34.25</v>
@@ -5322,16 +4641,16 @@
       <c r="L133">
         <v>2.1666666666666661</v>
       </c>
-      <c r="O133">
+      <c r="M133">
         <v>8.4166666666666661</v>
       </c>
-      <c r="P133">
+      <c r="N133">
         <v>8.3333333333333925E-2</v>
       </c>
     </row>
-    <row r="134" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E134">
         <v>21.857142857142858</v>
@@ -5357,16 +4676,16 @@
       <c r="L134">
         <v>2.1359677611434096</v>
       </c>
-      <c r="O134">
+      <c r="M134">
         <v>6.7619047619047619</v>
       </c>
-      <c r="P134">
+      <c r="N134">
         <v>2.0880558719208224</v>
       </c>
     </row>
-    <row r="135" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E135">
         <v>22.392857142857142</v>
@@ -5392,151 +4711,301 @@
       <c r="L135">
         <v>2.1422287438389267</v>
       </c>
-      <c r="O135">
+      <c r="M135" s="3">
         <v>6.333333333333333</v>
       </c>
-      <c r="P135">
+      <c r="N135">
         <v>6.8809523809523805</v>
       </c>
     </row>
-    <row r="136" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="136" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E136">
         <v>21.5</v>
       </c>
-      <c r="F136" t="e">
-        <v>#DIV/0!</v>
+      <c r="F136">
+        <v>0</v>
       </c>
       <c r="G136">
         <v>14</v>
       </c>
-      <c r="H136" t="e">
-        <v>#DIV/0!</v>
+      <c r="H136">
+        <v>0</v>
       </c>
       <c r="I136">
         <v>28.5</v>
       </c>
-      <c r="J136" t="e">
-        <v>#DIV/0!</v>
+      <c r="J136">
+        <v>0</v>
       </c>
       <c r="K136">
         <v>21.3333333333333</v>
       </c>
-      <c r="L136" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O136">
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" s="6">
         <v>7.3333333333333304</v>
       </c>
-      <c r="P136" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="137" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E137">
         <v>18.5</v>
       </c>
-      <c r="F137" t="e">
-        <v>#DIV/0!</v>
+      <c r="F137">
+        <v>0</v>
       </c>
       <c r="G137">
         <v>9</v>
       </c>
-      <c r="H137" t="e">
-        <v>#DIV/0!</v>
+      <c r="H137">
+        <v>0</v>
       </c>
       <c r="I137">
         <v>28</v>
       </c>
-      <c r="J137" t="e">
-        <v>#DIV/0!</v>
+      <c r="J137">
+        <v>0</v>
       </c>
       <c r="K137">
         <v>18.5</v>
       </c>
-      <c r="L137" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O137">
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
         <v>9.5</v>
       </c>
-      <c r="P137" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="138" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
+        <v>43</v>
+      </c>
+      <c r="E138">
+        <v>22.5</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>10.5</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>25</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>19.333333333333332</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D139" t="s">
+        <v>44</v>
+      </c>
+      <c r="E139">
+        <v>35.5</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>38.5</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>22.5</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>32.166666666666664</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D140" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="139" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D139" t="s">
+      <c r="E140">
+        <v>27.25</v>
+      </c>
+      <c r="F140">
+        <v>10.25</v>
+      </c>
+      <c r="G140">
+        <v>12.5</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
+        <v>25.5</v>
+      </c>
+      <c r="J140">
+        <v>2</v>
+      </c>
+      <c r="K140">
+        <v>21.75</v>
+      </c>
+      <c r="L140">
+        <v>2.4166666666666652</v>
+      </c>
+      <c r="M140">
+        <v>9.25</v>
+      </c>
+      <c r="N140">
+        <v>3.4166666666666652</v>
+      </c>
+    </row>
+    <row r="141" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D141" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="140" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D140" t="s">
+      <c r="E141">
+        <v>23</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>12</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>21.5</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>18.833333333333332</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141" s="1">
+        <v>6.833333333333333</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D142" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="141" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D141" t="s">
+      <c r="E142">
+        <v>20.75</v>
+      </c>
+      <c r="F142">
+        <v>2.75</v>
+      </c>
+      <c r="G142">
+        <v>10.75</v>
+      </c>
+      <c r="H142">
+        <v>1.75</v>
+      </c>
+      <c r="I142">
+        <v>27</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>19.5</v>
+      </c>
+      <c r="L142">
+        <v>0.33333333333333215</v>
+      </c>
+      <c r="M142">
+        <v>8.75</v>
+      </c>
+      <c r="N142">
+        <v>2.0833333333333286</v>
+      </c>
+    </row>
+    <row r="143" spans="4:15" x14ac:dyDescent="0.3">
+      <c r="D143" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="142" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D142" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="143" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D143" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="144" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D144" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="145" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D145" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="146" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D146" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="147" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D147" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="148" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D148" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="149" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D149" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="150" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E143">
+        <v>23.5</v>
+      </c>
+      <c r="F143">
+        <v>5.5</v>
+      </c>
+      <c r="G143">
+        <v>11.75</v>
+      </c>
+      <c r="H143">
+        <v>2.75</v>
+      </c>
+      <c r="I143">
+        <v>31.25</v>
+      </c>
+      <c r="J143">
+        <v>1.75</v>
+      </c>
+      <c r="K143">
+        <v>22.166666666666664</v>
+      </c>
+      <c r="L143">
+        <v>0.33333333333333393</v>
+      </c>
+      <c r="M143">
+        <v>10.416666666666666</v>
+      </c>
+      <c r="N143">
+        <v>3.0833333333333353</v>
+      </c>
+    </row>
+    <row r="150" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C150">
         <v>0.2</v>
       </c>
     </row>
-    <row r="151" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E151">
         <v>22.25</v>
@@ -5562,16 +5031,16 @@
       <c r="L151">
         <v>1.4166666666666661</v>
       </c>
-      <c r="O151">
+      <c r="M151">
         <v>2.6666666666666665</v>
       </c>
-      <c r="P151">
+      <c r="N151">
         <v>1.1666666666666665</v>
       </c>
     </row>
-    <row r="152" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E152">
         <v>12.5</v>
@@ -5591,22 +5060,22 @@
       <c r="J152">
         <v>0</v>
       </c>
-      <c r="K152">
+      <c r="K152" s="1">
         <v>13.333333333333334</v>
       </c>
       <c r="L152">
         <v>0</v>
       </c>
-      <c r="O152">
+      <c r="M152">
         <v>3.333333333333333</v>
       </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E153">
         <v>20</v>
@@ -5632,26 +5101,27 @@
       <c r="L153">
         <v>0</v>
       </c>
-      <c r="O153">
+      <c r="M153" s="1">
         <v>2.333333333333333</v>
       </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153" s="8"/>
+    </row>
+    <row r="154" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="155" spans="2:16" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="155" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C155">
         <v>0.05</v>
       </c>
     </row>
-    <row r="156" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E156">
         <v>24.45</v>
@@ -5677,16 +5147,16 @@
       <c r="L156">
         <v>2.5789987529855898</v>
       </c>
-      <c r="O156">
+      <c r="M156">
         <v>10.766666666666699</v>
       </c>
-      <c r="P156">
+      <c r="N156">
         <v>3.56959035585905</v>
       </c>
     </row>
-    <row r="157" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E157">
         <v>30.1</v>
@@ -5712,16 +5182,16 @@
       <c r="L157">
         <v>2.8722813232690099</v>
       </c>
-      <c r="O157">
+      <c r="M157">
         <v>13.5</v>
       </c>
-      <c r="P157">
+      <c r="N157">
         <v>3.0631219449089402</v>
       </c>
     </row>
-    <row r="158" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E158">
         <v>19</v>
@@ -5741,22 +5211,23 @@
       <c r="J158">
         <v>0.70710678118654802</v>
       </c>
-      <c r="K158">
+      <c r="K158" s="2">
         <v>14.1666666666667</v>
       </c>
       <c r="L158">
         <v>0.70710678118654802</v>
       </c>
-      <c r="O158">
+      <c r="M158" s="2">
         <v>7.1666666666666696</v>
       </c>
-      <c r="P158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158" s="7"/>
+    </row>
+    <row r="159" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E159">
         <v>21.1666666666667</v>
@@ -5776,22 +5247,23 @@
       <c r="J159">
         <v>2.1473497877875198</v>
       </c>
-      <c r="K159">
+      <c r="K159" s="1">
         <v>17.3333333333333</v>
       </c>
       <c r="L159">
         <v>1.6287350238076701</v>
       </c>
-      <c r="O159">
+      <c r="M159" s="1">
         <v>7.9444444444444402</v>
       </c>
-      <c r="P159">
+      <c r="N159">
         <v>2.8161242081192999</v>
       </c>
-    </row>
-    <row r="160" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O159" s="8"/>
+    </row>
+    <row r="160" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E160">
         <v>28.5</v>
@@ -5817,16 +5289,16 @@
       <c r="L160">
         <v>2.9876288132775</v>
       </c>
-      <c r="O160">
+      <c r="M160">
         <v>10.5555555555556</v>
       </c>
-      <c r="P160">
+      <c r="N160">
         <v>2.5239592648001201</v>
       </c>
     </row>
-    <row r="161" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="161" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E161">
         <v>29.5</v>
@@ -5852,16 +5324,16 @@
       <c r="L161">
         <v>1.70398045256278</v>
       </c>
-      <c r="O161">
+      <c r="M161">
         <v>11.3703703703704</v>
       </c>
-      <c r="P161">
+      <c r="N161">
         <v>2.2388268532899902</v>
       </c>
     </row>
-    <row r="162" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="162" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E162">
         <v>26.1875</v>
@@ -5887,16 +5359,16 @@
       <c r="L162">
         <v>4.40559737089586</v>
       </c>
-      <c r="O162">
+      <c r="M162" s="3">
         <v>4.083333333333333</v>
       </c>
-      <c r="P162">
+      <c r="N162">
         <v>1.609433992985664</v>
       </c>
     </row>
-    <row r="163" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="163" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E163">
         <v>25.375</v>
@@ -5922,16 +5394,16 @@
       <c r="L163">
         <v>1.2539866980510155</v>
       </c>
-      <c r="O163">
+      <c r="M163" s="3">
         <v>4.8541666666666661</v>
       </c>
-      <c r="P163">
+      <c r="N163">
         <v>3.9488372937134582</v>
       </c>
     </row>
-    <row r="164" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="164" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E164">
         <v>31.5</v>
@@ -5957,16 +5429,16 @@
       <c r="L164">
         <v>4.6215277256031477</v>
       </c>
-      <c r="O164">
+      <c r="M164" s="3">
         <v>7.3666666666666663</v>
       </c>
-      <c r="P164">
+      <c r="N164">
         <v>3.472217777774933</v>
       </c>
     </row>
-    <row r="165" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="165" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E165">
         <v>30.5</v>
@@ -5992,51 +5464,51 @@
       <c r="L165">
         <v>4.3863999515715992</v>
       </c>
-      <c r="O165">
+      <c r="M165">
         <v>8.4880952380952372</v>
       </c>
-      <c r="P165">
+      <c r="N165">
         <v>3.0831494705246421</v>
       </c>
     </row>
-    <row r="166" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="166" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E166">
         <v>22.5</v>
       </c>
-      <c r="F166" t="e">
-        <v>#DIV/0!</v>
+      <c r="F166">
+        <v>0</v>
       </c>
       <c r="G166">
         <v>21.5</v>
       </c>
-      <c r="H166" t="e">
-        <v>#DIV/0!</v>
+      <c r="H166">
+        <v>0</v>
       </c>
       <c r="I166">
         <v>9.5</v>
       </c>
-      <c r="J166" t="e">
-        <v>#DIV/0!</v>
+      <c r="J166">
+        <v>0</v>
       </c>
       <c r="K166">
         <v>17.8333333333333</v>
       </c>
-      <c r="L166" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O166">
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
         <v>8.3333333333333304</v>
       </c>
-      <c r="P166" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="167" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="N166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E167">
         <v>22.5</v>
@@ -6062,81 +5534,231 @@
       <c r="L167">
         <v>2.5276251480171799</v>
       </c>
-      <c r="O167">
+      <c r="M167">
         <v>8.78571428571429</v>
       </c>
-      <c r="P167">
+      <c r="N167">
         <v>2.5362451936947399</v>
       </c>
     </row>
-    <row r="168" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="168" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
+        <v>43</v>
+      </c>
+      <c r="E168">
+        <v>50</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>48.5</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>16.5</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>38.333333333333336</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>21.833333333333332</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D169" t="s">
+        <v>44</v>
+      </c>
+      <c r="E169">
+        <v>28.5</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>26.5</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>9.5</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>21.5</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>12</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D170" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="169" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D169" t="s">
+      <c r="E170">
+        <v>29.25</v>
+      </c>
+      <c r="F170">
+        <v>0.25</v>
+      </c>
+      <c r="G170">
+        <v>23</v>
+      </c>
+      <c r="H170">
+        <v>2.5</v>
+      </c>
+      <c r="I170">
+        <v>12.25</v>
+      </c>
+      <c r="J170">
+        <v>0.25</v>
+      </c>
+      <c r="K170">
+        <v>21.5</v>
+      </c>
+      <c r="L170">
+        <v>0.83333333333333215</v>
+      </c>
+      <c r="M170">
+        <v>9.25</v>
+      </c>
+      <c r="N170">
+        <v>1.0833333333333217</v>
+      </c>
+    </row>
+    <row r="171" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D171" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="170" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D170" t="s">
+      <c r="E171">
+        <v>22.5</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>26</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>10.5</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>19.666666666666668</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D172" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="171" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D171" t="s">
+      <c r="E172">
+        <v>29</v>
+      </c>
+      <c r="F172">
+        <v>0.40824829046386302</v>
+      </c>
+      <c r="G172">
+        <v>23</v>
+      </c>
+      <c r="H172">
+        <v>4.708148963941845</v>
+      </c>
+      <c r="I172">
+        <v>8.8333333333333339</v>
+      </c>
+      <c r="J172">
+        <v>1.1785113019775793</v>
+      </c>
+      <c r="K172">
+        <v>20.277777777777782</v>
+      </c>
+      <c r="L172">
+        <v>1.3425606637327305</v>
+      </c>
+      <c r="M172">
+        <v>11.444444444444443</v>
+      </c>
+      <c r="N172">
+        <v>2.1184084405486368</v>
+      </c>
+    </row>
+    <row r="173" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D173" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="172" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D172" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="173" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D173" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="174" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D174" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="175" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D175" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="176" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D176" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="177" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D177" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="178" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D178" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="179" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D179" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="180" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="E173">
+        <v>25.25</v>
+      </c>
+      <c r="F173">
+        <v>0.75</v>
+      </c>
+      <c r="G173">
+        <v>27.75</v>
+      </c>
+      <c r="H173">
+        <v>0.75</v>
+      </c>
+      <c r="I173">
+        <v>9.25</v>
+      </c>
+      <c r="J173">
+        <v>2.75</v>
+      </c>
+      <c r="K173">
+        <v>20.75</v>
+      </c>
+      <c r="L173">
+        <v>1.4166666666666679</v>
+      </c>
+      <c r="M173">
+        <v>11.5</v>
+      </c>
+      <c r="N173">
+        <v>1.3333333333333204</v>
+      </c>
+    </row>
+    <row r="180" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C180">
         <v>0.2</v>
       </c>
     </row>
-    <row r="181" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E181">
         <v>18.5</v>
@@ -6162,16 +5784,17 @@
       <c r="L181">
         <v>1.8333333333333264</v>
       </c>
-      <c r="O181">
+      <c r="M181" s="1">
         <v>3.6666666666666701</v>
       </c>
-      <c r="P181">
+      <c r="N181">
         <v>0.83333333333333448</v>
       </c>
-    </row>
-    <row r="182" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="O181" s="8"/>
+    </row>
+    <row r="182" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E182">
         <v>21</v>
@@ -6197,16 +5820,16 @@
       <c r="L182">
         <v>0</v>
       </c>
-      <c r="O182">
+      <c r="M182">
         <v>6.5</v>
       </c>
-      <c r="P182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="N182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E183">
         <v>18.5</v>
@@ -6226,16 +5849,16 @@
       <c r="J183">
         <v>0</v>
       </c>
-      <c r="K183">
+      <c r="K183" s="1">
         <v>13.5</v>
       </c>
       <c r="L183">
         <v>0</v>
       </c>
-      <c r="O183">
+      <c r="M183">
         <v>5.5</v>
       </c>
-      <c r="P183">
+      <c r="N183">
         <v>0</v>
       </c>
     </row>

--- a/DataAnalysis/DataAnalysis.xlsx
+++ b/DataAnalysis/DataAnalysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A9A717-FB68-4B97-91FF-3D7A6BF661FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2C9D37-EFCA-4F1A-8D93-82492F453DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{216728D3-2A76-4D61-AF39-758D90BA286A}"/>
   </bookViews>
@@ -724,14 +724,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1523,7 +1522,7 @@
       <c r="N9">
         <v>1.5444044759016899</v>
       </c>
-      <c r="O9" s="7"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
@@ -1874,7 +1873,7 @@
       <c r="N19">
         <v>0</v>
       </c>
-      <c r="O19" s="8"/>
+      <c r="O19" s="7"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
@@ -2055,7 +2054,7 @@
       <c r="N31">
         <v>1.25</v>
       </c>
-      <c r="O31" s="8"/>
+      <c r="O31" s="7"/>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
@@ -2206,7 +2205,7 @@
       <c r="N37">
         <v>2.89907392620982</v>
       </c>
-      <c r="O37" s="7"/>
+      <c r="O37" s="6"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
@@ -2312,7 +2311,7 @@
       <c r="N40">
         <v>2.53783104633722</v>
       </c>
-      <c r="O40" s="8"/>
+      <c r="O40" s="7"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
@@ -2843,7 +2842,7 @@
       <c r="N62">
         <v>0</v>
       </c>
-      <c r="O62" s="8"/>
+      <c r="O62" s="7"/>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
@@ -2959,7 +2958,7 @@
       <c r="N67">
         <v>1.0801234497346399</v>
       </c>
-      <c r="O67" s="7"/>
+      <c r="O67" s="6"/>
     </row>
     <row r="68" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
@@ -3310,7 +3309,7 @@
       <c r="N77">
         <v>0</v>
       </c>
-      <c r="O77" s="8"/>
+      <c r="O77" s="7"/>
     </row>
     <row r="78" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
@@ -3561,7 +3560,7 @@
       <c r="N91">
         <v>0</v>
       </c>
-      <c r="O91" s="8"/>
+      <c r="O91" s="7"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
@@ -3717,7 +3716,7 @@
       <c r="N98">
         <v>0.91792842454768298</v>
       </c>
-      <c r="O98" s="7"/>
+      <c r="O98" s="6"/>
     </row>
     <row r="99" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
@@ -3998,7 +3997,7 @@
       <c r="N106">
         <v>0</v>
       </c>
-      <c r="O106" s="8"/>
+      <c r="O106" s="7"/>
     </row>
     <row r="107" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
@@ -4284,7 +4283,7 @@
       <c r="N121">
         <v>0</v>
       </c>
-      <c r="O121" s="8"/>
+      <c r="O121" s="7"/>
     </row>
     <row r="122" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
@@ -4470,7 +4469,7 @@
       <c r="N128">
         <v>1.75066125073208</v>
       </c>
-      <c r="O128" s="7"/>
+      <c r="O128" s="6"/>
     </row>
     <row r="129" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
@@ -4506,7 +4505,7 @@
       <c r="N129">
         <v>3.4221951658382102</v>
       </c>
-      <c r="O129" s="8"/>
+      <c r="O129" s="7"/>
     </row>
     <row r="130" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
@@ -4746,7 +4745,7 @@
       <c r="L136">
         <v>0</v>
       </c>
-      <c r="M136" s="6">
+      <c r="M136">
         <v>7.3333333333333304</v>
       </c>
       <c r="N136">
@@ -5107,7 +5106,7 @@
       <c r="N153">
         <v>0</v>
       </c>
-      <c r="O153" s="8"/>
+      <c r="O153" s="7"/>
     </row>
     <row r="154" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
@@ -5223,7 +5222,7 @@
       <c r="N158">
         <v>0</v>
       </c>
-      <c r="O158" s="7"/>
+      <c r="O158" s="6"/>
     </row>
     <row r="159" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
@@ -5259,7 +5258,7 @@
       <c r="N159">
         <v>2.8161242081192999</v>
       </c>
-      <c r="O159" s="8"/>
+      <c r="O159" s="7"/>
     </row>
     <row r="160" spans="2:15" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
@@ -5790,7 +5789,7 @@
       <c r="N181">
         <v>0.83333333333333448</v>
       </c>
-      <c r="O181" s="8"/>
+      <c r="O181" s="7"/>
     </row>
     <row r="182" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
